--- a/assets/constructions/examples/ctd_tca.xlsx
+++ b/assets/constructions/examples/ctd_tca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,26 +599,46 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PTSNR 16CA-16</t>
+          <t>CSSPR10CA09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T-MaxⓇ P cartridge for turning</t>
+          <t>Cartridges</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PTSN</t>
+          <t>CSSP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +648,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -639,7 +659,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COR_TN1604_H</t>
+          <t>SP0903H</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -649,33 +669,37 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>TNMG 160408</t>
+          <t>SP..090308/SP..322</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ISO_5611:16AR</t>
+          <t>ISO_5611:10AR</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ISO_TN1604H</t>
+          <t>ISO_SP0903H</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>TSNR 16CA-16</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
+          <t>SSPR10CA09</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ZX</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -684,57 +708,65 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>55</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="V2" t="n">
+        <v>14</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>16</v>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA Catalog</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STFCR08CA-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>PSKNR 20CA-15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>T-MaxⓇ P cartridge for turning</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>STFC</t>
+          <t>PSKN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -744,18 +776,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TC09T3H</t>
+          <t>COR_SN1506_H</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -763,21 +795,25 @@
           <t>ISO</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SNMG 150612</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ISO_5611:8AR</t>
+          <t>ISO_5611:20AR</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ISO_TC09T3H</t>
+          <t>ISO_SN1506H</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>TFCR08CA-09</t>
+          <t>SKNR 20CA-15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -787,7 +823,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -796,22 +832,24 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>20</v>
+      </c>
       <c r="AB3" t="n">
         <v>1</v>
       </c>
@@ -819,16 +857,22 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.219</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -838,7 +882,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PTSNR 12CA-16</t>
+          <t>PTGNL 16CA-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -848,7 +892,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTSN</t>
+          <t>PTGN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -862,10 +906,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -884,7 +928,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ISO_5611:12AR</t>
+          <t>ISO_5611:16AL</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -895,13 +939,13 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>TSNR 12CA-16</t>
+          <t>TGNL 16CA-16</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -914,14 +958,14 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="X4" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -930,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
@@ -939,7 +983,7 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.101</v>
+        <v>0.178</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -949,6 +993,12 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -958,7 +1008,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PTSNL 12CA-16</t>
+          <t>PSRNL 20CA-15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -968,7 +1018,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PTSN</t>
+          <t>PSRN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -982,14 +1032,14 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COR_TN1604_H</t>
+          <t>COR_SN1506_H</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -999,23 +1049,23 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TNMG 160408</t>
+          <t>SNMG 150612</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ISO_5611:12AL</t>
+          <t>ISO_5611:20AR</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ISO_TN1604H</t>
+          <t>ISO_SN1506H</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>TSNL 12CA-16</t>
+          <t>SRNL 20CA-15</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1034,23 +1084,23 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="X5" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
@@ -1059,7 +1109,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.222</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1069,26 +1119,32 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PSRNR 20CA-15</t>
+          <t>SCLCR12CA12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T-MaxⓇ P cartridge for turning</t>
+          <t>Cartridges</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PSRN</t>
+          <t>SCLC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1098,18 +1154,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COR_SN1506_H</t>
+          <t>CN1204H</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1119,33 +1175,37 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SNMG 150612</t>
+          <t>CN..120408/CN..434</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ISO_5611:20AR</t>
+          <t>ISO_5611:12AR</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ISO_SN1506H</t>
+          <t>ISO_CN1204H</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>SRNR 20CA-15</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>CLCR12CA12</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ZX</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1154,41 +1214,45 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>70</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
-        <v>25</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="V6" t="n">
+        <v>20</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="n">
-        <v>20</v>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
         <v>1</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="n">
-        <v>0.224</v>
-      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA Catalog</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
